--- a/Data/EC/NIT-9009103874.xlsx
+++ b/Data/EC/NIT-9009103874.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF4B5848-760B-48C0-B2A2-CDE0217772F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{435CD754-DF2C-46E3-8EFA-3FC1AFC4E339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6BDDF69E-2A8A-4690-AA1E-1932948C8CD2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D9BC8443-A1CE-4459-BD9C-F9F5EA746020}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -92,133 +92,133 @@
     <t>JOSE GREGORIO RICO OROZCO</t>
   </si>
   <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
     <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -262,7 +262,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,9 +317,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -332,7 +330,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -532,23 +532,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -576,10 +576,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -617,22 +617,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>496450</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>259200</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46805B63-A8F1-1A58-1405-A38FDA3EC4D6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C6A13EF-AEA3-57AA-F931-067D9EC8C2F9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -654,7 +654,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="750450" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -983,23 +983,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF9385F4-A852-4029-9951-A880E81E7907}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C624DBC9-E031-4B08-BDBE-D0A6AAE24FE9}">
   <dimension ref="B2:J68"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="16.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1012,7 +1012,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1023,7 +1023,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1034,7 +1034,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1045,8 +1045,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1"/>
-    <row r="7" spans="2:10">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>62</v>
       </c>
@@ -1061,8 +1061,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1"/>
-    <row r="9" spans="2:10">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1077,8 +1077,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1"/>
-    <row r="11" spans="2:10">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
@@ -1093,8 +1093,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1"/>
-    <row r="13" spans="2:10">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>64</v>
       </c>
@@ -1113,7 +1113,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1165,7 +1165,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1188,7 +1188,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1211,7 +1211,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1222,10 +1222,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F19" s="18">
-        <v>27578</v>
+        <v>20656</v>
       </c>
       <c r="G19" s="18">
         <v>737717</v>
@@ -1234,7 +1234,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1245,7 +1245,7 @@
         <v>17</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" s="18">
         <v>29509</v>
@@ -1257,7 +1257,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>17</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="18">
         <v>29509</v>
@@ -1280,7 +1280,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>17</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22" s="18">
         <v>29509</v>
@@ -1303,7 +1303,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="18">
         <v>29509</v>
@@ -1326,7 +1326,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>17</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F24" s="18">
         <v>29509</v>
@@ -1349,7 +1349,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>17</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" s="18">
         <v>29509</v>
@@ -1372,7 +1372,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F26" s="18">
         <v>29509</v>
@@ -1395,7 +1395,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>17</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F27" s="18">
         <v>29509</v>
@@ -1418,7 +1418,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>17</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F28" s="18">
         <v>29509</v>
@@ -1441,7 +1441,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>17</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F29" s="18">
         <v>29509</v>
@@ -1464,7 +1464,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F30" s="18">
         <v>29509</v>
@@ -1487,7 +1487,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F31" s="18">
         <v>29509</v>
@@ -1510,7 +1510,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F32" s="18">
         <v>29509</v>
@@ -1533,7 +1533,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F33" s="18">
         <v>29509</v>
@@ -1556,7 +1556,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1567,7 +1567,7 @@
         <v>17</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F34" s="18">
         <v>29509</v>
@@ -1579,7 +1579,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>17</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F35" s="18">
         <v>29509</v>
@@ -1602,7 +1602,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1613,7 +1613,7 @@
         <v>17</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F36" s="18">
         <v>29509</v>
@@ -1625,7 +1625,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>17</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F37" s="18">
         <v>29509</v>
@@ -1648,7 +1648,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1659,7 +1659,7 @@
         <v>17</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F38" s="18">
         <v>29509</v>
@@ -1671,7 +1671,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F39" s="18">
         <v>29509</v>
@@ -1694,7 +1694,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F40" s="18">
         <v>29509</v>
@@ -1717,7 +1717,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>17</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F41" s="18">
         <v>29509</v>
@@ -1740,7 +1740,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1751,7 +1751,7 @@
         <v>17</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F42" s="18">
         <v>29509</v>
@@ -1763,7 +1763,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>17</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F43" s="18">
         <v>29509</v>
@@ -1786,7 +1786,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>17</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F44" s="18">
         <v>29509</v>
@@ -1809,7 +1809,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>17</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F45" s="18">
         <v>29509</v>
@@ -1832,7 +1832,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1843,7 +1843,7 @@
         <v>17</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F46" s="18">
         <v>29509</v>
@@ -1855,7 +1855,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>17</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F47" s="18">
         <v>29509</v>
@@ -1878,7 +1878,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>17</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F48" s="18">
         <v>29509</v>
@@ -1901,7 +1901,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>17</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F49" s="18">
         <v>29509</v>
@@ -1924,7 +1924,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1935,7 +1935,7 @@
         <v>17</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F50" s="18">
         <v>29509</v>
@@ -1947,7 +1947,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>17</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F51" s="18">
         <v>29509</v>
@@ -1970,7 +1970,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>17</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F52" s="18">
         <v>29509</v>
@@ -1993,7 +1993,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>17</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F53" s="18">
         <v>29509</v>
@@ -2016,7 +2016,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>17</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F54" s="18">
         <v>29509</v>
@@ -2039,7 +2039,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>17</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F55" s="18">
         <v>29509</v>
@@ -2062,7 +2062,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>17</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F56" s="18">
         <v>29509</v>
@@ -2085,7 +2085,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>17</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F57" s="18">
         <v>29509</v>
@@ -2108,7 +2108,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>17</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F58" s="18">
         <v>29509</v>
@@ -2131,7 +2131,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>17</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F59" s="18">
         <v>29509</v>
@@ -2154,7 +2154,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>17</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F60" s="18">
         <v>29509</v>
@@ -2177,7 +2177,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>17</v>
       </c>
       <c r="E61" s="16" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F61" s="18">
         <v>29509</v>
@@ -2200,7 +2200,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="21" t="s">
         <v>8</v>
       </c>
@@ -2211,10 +2211,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="22" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="F62" s="24">
-        <v>20656</v>
+        <v>27578</v>
       </c>
       <c r="G62" s="24">
         <v>737717</v>
@@ -2223,7 +2223,7 @@
       <c r="I62" s="25"/>
       <c r="J62" s="26"/>
     </row>
-    <row r="67" spans="2:10">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="32" t="s">
         <v>70</v>
       </c>
@@ -2234,7 +2234,7 @@
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="2:10">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="32" t="s">
         <v>69</v>
       </c>
